--- a/tame_output/ON/bt/strategyON_20230724.xlsx
+++ b/tame_output/ON/bt/strategyON_20230724.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>457.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>105.0%</t>
+          <t>104.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.9%</t>
+          <t>141.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>136.3%</t>
+          <t>135.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1667"/>
+  <dimension ref="A1:G1668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39851,7 +39851,7 @@
         <v>45129</v>
       </c>
       <c r="B1667" t="n">
-        <v>2.900002805408948</v>
+        <v>2.89939150368406</v>
       </c>
       <c r="C1667" t="n">
         <v>3.010144445465673</v>
@@ -39867,6 +39867,29 @@
       </c>
       <c r="G1667" t="n">
         <v>4.28079688354429</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="2" t="n">
+        <v>45130</v>
+      </c>
+      <c r="B1668" t="n">
+        <v>2.894891024385695</v>
+      </c>
+      <c r="C1668" t="n">
+        <v>3.003340075840882</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>1.507972435932392</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>3.606172625900092</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>2.117754063464357</v>
+      </c>
+      <c r="G1668" t="n">
+        <v>4.273992513919498</v>
       </c>
     </row>
   </sheetData>
